--- a/Data/National Accounts/PSA-06IOG_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-06IOG_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4176D920-2E99-4C8B-B7AB-B98E9D11AF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6E8CD-C943-4901-9558-70D94E8C0238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IOG" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -292,6 +289,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -421,15 +421,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -741,7 +733,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -751,7 +743,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -953,10 +945,10 @@
         <v>1201246.8423382374</v>
       </c>
       <c r="Z12" s="8">
-        <v>1317598.5309524143</v>
+        <v>1317631.9349821862</v>
       </c>
       <c r="AA12" s="8">
-        <v>1513759.6199159236</v>
+        <v>1519464.1615540336</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -1105,10 +1097,10 @@
         <v>649888.23050803249</v>
       </c>
       <c r="Z13" s="11">
-        <v>668179.08655934699</v>
+        <v>668224.87875589449</v>
       </c>
       <c r="AA13" s="11">
-        <v>796224.60769312282</v>
+        <v>798414.54207227484</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -1257,10 +1249,10 @@
         <v>180668.09211822588</v>
       </c>
       <c r="Z14" s="11">
-        <v>223053.47217176005</v>
+        <v>223088.39124033193</v>
       </c>
       <c r="AA14" s="11">
-        <v>249853.00450830103</v>
+        <v>250362.48052838616</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -1409,10 +1401,10 @@
         <v>14645.851081385646</v>
       </c>
       <c r="Z15" s="11">
-        <v>13642.968937726615</v>
+        <v>13652.370416184236</v>
       </c>
       <c r="AA15" s="11">
-        <v>14161.946021615307</v>
+        <v>14235.257421974988</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -1561,10 +1553,10 @@
         <v>69473.644458333772</v>
       </c>
       <c r="Z16" s="11">
-        <v>100983.53954152006</v>
+        <v>100835.08728591836</v>
       </c>
       <c r="AA16" s="11">
-        <v>106073.83492038577</v>
+        <v>107659.63718996514</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -1713,10 +1705,10 @@
         <v>92354.5676057237</v>
       </c>
       <c r="Z17" s="11">
-        <v>103398.20085399944</v>
+        <v>103428.18606185616</v>
       </c>
       <c r="AA17" s="11">
-        <v>106951.93566706186</v>
+        <v>107535.57501233582</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -1865,10 +1857,10 @@
         <v>102583.73488821456</v>
       </c>
       <c r="Z18" s="11">
-        <v>112183.22890289527</v>
+        <v>112187.66384161804</v>
       </c>
       <c r="AA18" s="11">
-        <v>131785.46093974129</v>
+        <v>131776.40755005862</v>
       </c>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
@@ -2017,10 +2009,10 @@
         <v>69839.930572494777</v>
       </c>
       <c r="Z19" s="11">
-        <v>73409.348269667447</v>
+        <v>73456.680253899525</v>
       </c>
       <c r="AA19" s="11">
-        <v>83652.169248914986</v>
+        <v>84275.058318842988</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -2169,10 +2161,10 @@
         <v>17876.355608203779</v>
       </c>
       <c r="Z20" s="11">
-        <v>18857.813010723941</v>
+        <v>18866.661382422208</v>
       </c>
       <c r="AA20" s="11">
-        <v>20768.470360118594</v>
+        <v>20893.561312826729</v>
       </c>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
@@ -2321,10 +2313,10 @@
         <v>3916.4354976229015</v>
       </c>
       <c r="Z21" s="11">
-        <v>3890.8727047744646</v>
+        <v>3892.0157440614203</v>
       </c>
       <c r="AA21" s="11">
-        <v>4288.1905566616124</v>
+        <v>4311.6421473682867</v>
       </c>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
@@ -2473,10 +2465,10 @@
         <v>1433415.7538270983</v>
       </c>
       <c r="Z22" s="11">
-        <v>1415661.7755286773</v>
+        <v>1416236.3269338622</v>
       </c>
       <c r="AA22" s="11">
-        <v>1235839.4799872381</v>
+        <v>1236982.5946523985</v>
       </c>
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
@@ -2625,10 +2617,10 @@
         <v>353670.46513613086</v>
       </c>
       <c r="Z23" s="11">
-        <v>370683.69229035953</v>
+        <v>370917.90417037543</v>
       </c>
       <c r="AA23" s="11">
-        <v>411212.75216915883</v>
+        <v>415411.57773895393</v>
       </c>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9"/>
@@ -2777,10 +2769,10 @@
         <v>89130.575922980119</v>
       </c>
       <c r="Z24" s="11">
-        <v>89714.37625381691</v>
+        <v>89974.075325842918</v>
       </c>
       <c r="AA24" s="11">
-        <v>92736.141636736138</v>
+        <v>94101.385290898848</v>
       </c>
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
@@ -2929,10 +2921,10 @@
         <v>397432.07768558152</v>
       </c>
       <c r="Z25" s="11">
-        <v>463450.16508385743</v>
+        <v>464491.01646714087</v>
       </c>
       <c r="AA25" s="11">
-        <v>480022.23096823454</v>
+        <v>482532.89096400631</v>
       </c>
       <c r="AB25" s="9"/>
       <c r="AC25" s="9"/>
@@ -3081,10 +3073,10 @@
         <v>796370.53956461279</v>
       </c>
       <c r="Z26" s="11">
-        <v>749952.86461706413</v>
+        <v>750920.67411957111</v>
       </c>
       <c r="AA26" s="11">
-        <v>836323.28842136881</v>
+        <v>846309.21327203151</v>
       </c>
       <c r="AB26" s="9"/>
       <c r="AC26" s="9"/>
@@ -3233,10 +3225,10 @@
         <v>75087.532118645875</v>
       </c>
       <c r="Z27" s="11">
-        <v>75829.432870347635</v>
+        <v>75897.947195073473</v>
       </c>
       <c r="AA27" s="11">
-        <v>76318.684808399979</v>
+        <v>77741.219990738828</v>
       </c>
       <c r="AB27" s="9"/>
       <c r="AC27" s="9"/>
@@ -3385,10 +3377,10 @@
         <v>210890.36576988074</v>
       </c>
       <c r="Z28" s="11">
-        <v>211276.82028727501</v>
+        <v>211362.82495421471</v>
       </c>
       <c r="AA28" s="11">
-        <v>271471.6649662946</v>
+        <v>277089.59294476156</v>
       </c>
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
@@ -3537,10 +3529,10 @@
         <v>340920.55144926533</v>
       </c>
       <c r="Z29" s="11">
-        <v>358519.77329703537</v>
+        <v>358833.79339985043</v>
       </c>
       <c r="AA29" s="11">
-        <v>383822.90481975727</v>
+        <v>386585.32126378862</v>
       </c>
       <c r="AB29" s="9"/>
       <c r="AC29" s="9"/>
@@ -3689,10 +3681,10 @@
         <v>243416.30362843978</v>
       </c>
       <c r="Z30" s="11">
-        <v>311946.49363065494</v>
+        <v>311946.61553672794</v>
       </c>
       <c r="AA30" s="11">
-        <v>252810.00771674173</v>
+        <v>254001.28840450148</v>
       </c>
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
@@ -3844,7 +3836,7 @@
         <v>86195.473018558056</v>
       </c>
       <c r="AA31" s="11">
-        <v>95391.4225968549</v>
+        <v>95761.046878482419</v>
       </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -3993,10 +3985,10 @@
         <v>188200.81741650059</v>
       </c>
       <c r="Z32" s="11">
-        <v>206085.08351497579</v>
+        <v>206123.32188566058</v>
       </c>
       <c r="AA32" s="11">
-        <v>210084.81864232873</v>
+        <v>211364.25805124082</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
@@ -4145,10 +4137,10 @@
         <v>81091.489015745319</v>
       </c>
       <c r="Z33" s="11">
-        <v>88320.415578123211</v>
+        <v>88330.386308709465</v>
       </c>
       <c r="AA33" s="11">
-        <v>84975.506760608972</v>
+        <v>85317.274549306108</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -4297,10 +4289,10 @@
         <v>119351.59293524179</v>
       </c>
       <c r="Z34" s="11">
-        <v>119398.24858901893</v>
+        <v>119408.43082066081</v>
       </c>
       <c r="AA34" s="11">
-        <v>99300.112621360226</v>
+        <v>100365.96467505144</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -4449,10 +4441,10 @@
         <v>90049.584841319767</v>
       </c>
       <c r="Z35" s="11">
-        <v>94608.407123462355</v>
+        <v>94612.864369804884</v>
       </c>
       <c r="AA35" s="11">
-        <v>19867.843704347557</v>
+        <v>20579.921664945865</v>
       </c>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -4601,10 +4593,10 @@
         <v>146557.92867908609</v>
       </c>
       <c r="Z36" s="11">
-        <v>161837.92527514277</v>
+        <v>162062.34787715162</v>
       </c>
       <c r="AA36" s="11">
-        <v>203352.68549732323</v>
+        <v>205158.47162944684</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -4753,10 +4745,10 @@
         <v>158429.06497300428</v>
       </c>
       <c r="Z37" s="11">
-        <v>179112.02149275818</v>
+        <v>179128.46787465221</v>
       </c>
       <c r="AA37" s="11">
-        <v>189534.90020496375</v>
+        <v>190725.06399625784</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -4905,10 +4897,10 @@
         <v>88767.247520943449</v>
       </c>
       <c r="Z38" s="11">
-        <v>103483.31409626064</v>
+        <v>103485.12842253517</v>
       </c>
       <c r="AA38" s="11">
-        <v>122397.86823312854</v>
+        <v>122908.9903400871</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -5057,10 +5049,10 @@
         <v>88732.405267489405</v>
       </c>
       <c r="Z39" s="11">
-        <v>84882.337696423041</v>
+        <v>84916.118550981075</v>
       </c>
       <c r="AA39" s="11">
-        <v>101081.05367268116</v>
+        <v>101531.11590418042</v>
       </c>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
@@ -5209,10 +5201,10 @@
         <v>50407.379506891899</v>
       </c>
       <c r="Z40" s="11">
-        <v>54738.310765376271</v>
+        <v>54746.414922159347</v>
       </c>
       <c r="AA40" s="11">
-        <v>57605.397783348832</v>
+        <v>57725.331292139272</v>
       </c>
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
@@ -5361,10 +5353,10 @@
         <v>1689297.9821251857</v>
       </c>
       <c r="Z41" s="11">
-        <v>1751189.8205029774</v>
+        <v>1753805.8649521903</v>
       </c>
       <c r="AA41" s="11">
-        <v>1980122.0134982062</v>
+        <v>1993728.4239156074</v>
       </c>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
@@ -5610,10 +5602,10 @@
         <v>7922614.0034071263</v>
       </c>
       <c r="Z43" s="8">
-        <v>8294485.2824645787</v>
+        <v>8301027.9320879076</v>
       </c>
       <c r="AA43" s="8">
-        <v>8718030.3986250069</v>
+        <v>8775385.1089728586</v>
       </c>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -5925,7 +5917,7 @@
     </row>
     <row r="50" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:96" x14ac:dyDescent="0.2">
@@ -5935,7 +5927,7 @@
     </row>
     <row r="53" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:96" x14ac:dyDescent="0.2">
@@ -6137,10 +6129,10 @@
         <v>1125454.7119099684</v>
       </c>
       <c r="Z59" s="8">
-        <v>1207294.5891577296</v>
+        <v>1207326.8657925604</v>
       </c>
       <c r="AA59" s="8">
-        <v>1374963.4854924937</v>
+        <v>1372767.0376576039</v>
       </c>
       <c r="AB59" s="9"/>
       <c r="AC59" s="9"/>
@@ -6289,10 +6281,10 @@
         <v>616338.26059996407</v>
       </c>
       <c r="Z60" s="11">
-        <v>618226.651965786</v>
+        <v>618272.40415210999</v>
       </c>
       <c r="AA60" s="11">
-        <v>737305.23977975687</v>
+        <v>733402.40371061489</v>
       </c>
       <c r="AB60" s="9"/>
       <c r="AC60" s="9"/>
@@ -6441,10 +6433,10 @@
         <v>177182.3661201314</v>
       </c>
       <c r="Z61" s="11">
-        <v>219009.98636394032</v>
+        <v>219044.84462631645</v>
       </c>
       <c r="AA61" s="11">
-        <v>238827.3270180999</v>
+        <v>238574.11970863765</v>
       </c>
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
@@ -6593,10 +6585,10 @@
         <v>13570.897146418476</v>
       </c>
       <c r="Z62" s="11">
-        <v>13354.915441673211</v>
+        <v>13365.277218037938</v>
       </c>
       <c r="AA62" s="11">
-        <v>13112.506869153771</v>
+        <v>13150.275879211291</v>
       </c>
       <c r="AB62" s="9"/>
       <c r="AC62" s="9"/>
@@ -6745,10 +6737,10 @@
         <v>59814.016832506779</v>
       </c>
       <c r="Z63" s="11">
-        <v>87223.690593513107</v>
+        <v>87095.54676454555</v>
       </c>
       <c r="AA63" s="11">
-        <v>91412.285273761241</v>
+        <v>92579.029367133044</v>
       </c>
       <c r="AB63" s="9"/>
       <c r="AC63" s="9"/>
@@ -6897,10 +6889,10 @@
         <v>82664.102104325313</v>
       </c>
       <c r="Z64" s="11">
-        <v>87160.276249406554</v>
+        <v>87187.533637608198</v>
       </c>
       <c r="AA64" s="11">
-        <v>85705.934886369854</v>
+        <v>86052.216534111518</v>
       </c>
       <c r="AB64" s="9"/>
       <c r="AC64" s="9"/>
@@ -7049,10 +7041,10 @@
         <v>97088.032305060362</v>
       </c>
       <c r="Z65" s="11">
-        <v>100816.76261935807</v>
+        <v>100821.59631616702</v>
       </c>
       <c r="AA65" s="11">
-        <v>126801.06579417626</v>
+        <v>126788.0862492304</v>
       </c>
       <c r="AB65" s="9"/>
       <c r="AC65" s="9"/>
@@ -7201,10 +7193,10 @@
         <v>58996.079450188787</v>
       </c>
       <c r="Z66" s="11">
-        <v>62004.737714482435</v>
+        <v>62033.612112851966</v>
       </c>
       <c r="AA66" s="11">
-        <v>62190.750348735208</v>
+        <v>62465.678424332829</v>
       </c>
       <c r="AB66" s="9"/>
       <c r="AC66" s="9"/>
@@ -7353,10 +7345,10 @@
         <v>16441.014728425856</v>
       </c>
       <c r="Z67" s="11">
-        <v>16430.817868146456</v>
+        <v>16438.495265687663</v>
       </c>
       <c r="AA67" s="11">
-        <v>16362.396274810875</v>
+        <v>16495.411643746887</v>
       </c>
       <c r="AB67" s="9"/>
       <c r="AC67" s="9"/>
@@ -7505,10 +7497,10 @@
         <v>3359.9426229472074</v>
       </c>
       <c r="Z68" s="11">
-        <v>3066.7503414234852</v>
+        <v>3067.5556992356605</v>
       </c>
       <c r="AA68" s="11">
-        <v>3245.9792476298708</v>
+        <v>3259.8161405855085</v>
       </c>
       <c r="AB68" s="9"/>
       <c r="AC68" s="9"/>
@@ -7657,10 +7649,10 @@
         <v>957166.68378763576</v>
       </c>
       <c r="Z69" s="11">
-        <v>961584.7002067077</v>
+        <v>961869.8386811961</v>
       </c>
       <c r="AA69" s="11">
-        <v>945390.73157336167</v>
+        <v>937050.72501457157</v>
       </c>
       <c r="AB69" s="9"/>
       <c r="AC69" s="9"/>
@@ -7809,10 +7801,10 @@
         <v>297950.93489431543</v>
       </c>
       <c r="Z70" s="11">
-        <v>296387.63397582876</v>
+        <v>296575.35957990331</v>
       </c>
       <c r="AA70" s="11">
-        <v>313613.30141847464</v>
+        <v>316814.02726796002</v>
       </c>
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
@@ -7961,10 +7953,10 @@
         <v>72404.880570163281</v>
       </c>
       <c r="Z71" s="11">
-        <v>78528.71154426779</v>
+        <v>78730.610202742668</v>
       </c>
       <c r="AA71" s="11">
-        <v>70962.030641104298</v>
+        <v>72132.257917468727</v>
       </c>
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
@@ -8113,10 +8105,10 @@
         <v>284932.72699243471</v>
       </c>
       <c r="Z72" s="11">
-        <v>302366.14400715777</v>
+        <v>303096.02217712381</v>
       </c>
       <c r="AA72" s="11">
-        <v>278278.39208609128</v>
+        <v>279447.59239802079</v>
       </c>
       <c r="AB72" s="9"/>
       <c r="AC72" s="9"/>
@@ -8265,10 +8257,10 @@
         <v>642735.23853668745</v>
       </c>
       <c r="Z73" s="11">
-        <v>549809.08694432455</v>
+        <v>550532.55825324741</v>
       </c>
       <c r="AA73" s="11">
-        <v>598518.43167073233</v>
+        <v>605174.66423143912</v>
       </c>
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
@@ -8417,10 +8409,10 @@
         <v>72355.321969068638</v>
       </c>
       <c r="Z74" s="11">
-        <v>72727.235212249943</v>
+        <v>72775.06478598676</v>
       </c>
       <c r="AA74" s="11">
-        <v>70810.334640943314</v>
+        <v>71956.943999969924</v>
       </c>
       <c r="AB74" s="9"/>
       <c r="AC74" s="9"/>
@@ -8569,10 +8561,10 @@
         <v>171943.94464017038</v>
       </c>
       <c r="Z75" s="11">
-        <v>166530.26026194557</v>
+        <v>166602.44854355248</v>
       </c>
       <c r="AA75" s="11">
-        <v>209789.30102221147</v>
+        <v>214207.74767354853</v>
       </c>
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
@@ -8721,10 +8713,10 @@
         <v>289378.89956695522</v>
       </c>
       <c r="Z76" s="11">
-        <v>294459.31169524061</v>
+        <v>294714.8847936606</v>
       </c>
       <c r="AA76" s="11">
-        <v>305830.28491003113</v>
+        <v>308192.8376711029</v>
       </c>
       <c r="AB76" s="9"/>
       <c r="AC76" s="9"/>
@@ -8873,10 +8865,10 @@
         <v>136215.54893583036</v>
       </c>
       <c r="Z77" s="11">
-        <v>175778.86109763739</v>
+        <v>175778.96903282835</v>
       </c>
       <c r="AA77" s="11">
-        <v>171783.18702521571</v>
+        <v>172258.03286218771</v>
       </c>
       <c r="AB77" s="9"/>
       <c r="AC77" s="9"/>
@@ -9028,7 +9020,7 @@
         <v>52875.323891614549</v>
       </c>
       <c r="AA78" s="11">
-        <v>52982.385370341006</v>
+        <v>53130.987327067123</v>
       </c>
       <c r="AB78" s="9"/>
       <c r="AC78" s="9"/>
@@ -9177,10 +9169,10 @@
         <v>161441.96557933991</v>
       </c>
       <c r="Z79" s="11">
-        <v>175979.79465135201</v>
+        <v>176013.05482035762</v>
       </c>
       <c r="AA79" s="11">
-        <v>167900.22010979394</v>
+        <v>168840.6632584687</v>
       </c>
       <c r="AB79" s="9"/>
       <c r="AC79" s="9"/>
@@ -9329,10 +9321,10 @@
         <v>64683.060033550959</v>
       </c>
       <c r="Z80" s="11">
-        <v>68397.436232618347</v>
+        <v>68406.333432995307</v>
       </c>
       <c r="AA80" s="11">
-        <v>64940.605285972182</v>
+        <v>64651.484282474441</v>
       </c>
       <c r="AB80" s="9"/>
       <c r="AC80" s="9"/>
@@ -9481,10 +9473,10 @@
         <v>70068.961976601087</v>
       </c>
       <c r="Z81" s="11">
-        <v>83569.949680234335</v>
+        <v>83578.062150067213</v>
       </c>
       <c r="AA81" s="11">
-        <v>68287.511761641086</v>
+        <v>68881.64420396254</v>
       </c>
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
@@ -9633,10 +9625,10 @@
         <v>61581.65012195726</v>
       </c>
       <c r="Z82" s="11">
-        <v>54979.37167141767</v>
+        <v>54981.039940698669</v>
       </c>
       <c r="AA82" s="11">
-        <v>17898.885579996724</v>
+        <v>18226.045392601092</v>
       </c>
       <c r="AB82" s="9"/>
       <c r="AC82" s="9"/>
@@ -9785,10 +9777,10 @@
         <v>112826.6471724077</v>
       </c>
       <c r="Z83" s="11">
-        <v>117573.48460878219</v>
+        <v>117666.89861440627</v>
       </c>
       <c r="AA83" s="11">
-        <v>137296.70265788437</v>
+        <v>138581.11333353457</v>
       </c>
       <c r="AB83" s="9"/>
       <c r="AC83" s="9"/>
@@ -9937,10 +9929,10 @@
         <v>144355.0117572872</v>
       </c>
       <c r="Z84" s="11">
-        <v>155610.77841425937</v>
+        <v>155625.69509003044</v>
       </c>
       <c r="AA84" s="11">
-        <v>166197.72656881012</v>
+        <v>167789.86289179098</v>
       </c>
       <c r="AB84" s="9"/>
       <c r="AC84" s="9"/>
@@ -10089,10 +10081,10 @@
         <v>61953.902748374567</v>
       </c>
       <c r="Z85" s="11">
-        <v>63296.868216820578</v>
+        <v>63298.076775224989</v>
       </c>
       <c r="AA85" s="11">
-        <v>70535.230170227209</v>
+        <v>70730.554798581012</v>
       </c>
       <c r="AB85" s="9"/>
       <c r="AC85" s="9"/>
@@ -10241,10 +10233,10 @@
         <v>85192.570735247806</v>
       </c>
       <c r="Z86" s="11">
-        <v>78127.93156453775</v>
+        <v>78161.71641290735</v>
       </c>
       <c r="AA86" s="11">
-        <v>90405.908180778351</v>
+        <v>90818.551970639674</v>
       </c>
       <c r="AB86" s="9"/>
       <c r="AC86" s="9"/>
@@ -10393,10 +10385,10 @@
         <v>63436.819824848135</v>
       </c>
       <c r="Z87" s="11">
-        <v>65147.781732156807</v>
+        <v>65157.163313412471</v>
       </c>
       <c r="AA87" s="11">
-        <v>67853.967974982312</v>
+        <v>67882.519625301677</v>
       </c>
       <c r="AB87" s="9"/>
       <c r="AC87" s="9"/>
@@ -10545,10 +10537,10 @@
         <v>1219069.556296428</v>
       </c>
       <c r="Z88" s="11">
-        <v>1239637.7489729165</v>
+        <v>1244434.2152747228</v>
       </c>
       <c r="AA88" s="11">
-        <v>1312614.0142140312</v>
+        <v>1303857.8627155169</v>
       </c>
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
@@ -10794,10 +10786,10 @@
         <v>6147066.6267299727</v>
       </c>
       <c r="Z90" s="8">
-        <v>6260663.0037398003</v>
+        <v>6268200.20155924</v>
       </c>
       <c r="AA90" s="8">
-        <v>6556852.6383551182</v>
+        <v>6563393.1564938109</v>
       </c>
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
@@ -11109,7 +11101,7 @@
     </row>
     <row r="97" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:91" x14ac:dyDescent="0.2">
@@ -11119,7 +11111,7 @@
     </row>
     <row r="100" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:91" x14ac:dyDescent="0.2">
@@ -11235,7 +11227,7 @@
         <v>74</v>
       </c>
       <c r="Z104" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA104" s="16"/>
     </row>
@@ -11316,10 +11308,10 @@
         <v>-9.3310366702204419</v>
       </c>
       <c r="Y106" s="17">
-        <v>9.6859100489036223</v>
+        <v>9.6886908287229403</v>
       </c>
       <c r="Z106" s="17">
-        <v>14.887773806313831</v>
+        <v>15.317800154454829</v>
       </c>
       <c r="AA106" s="17"/>
       <c r="AB106" s="9"/>
@@ -11461,10 +11453,10 @@
         <v>-11.894687336042622</v>
       </c>
       <c r="Y107" s="17">
-        <v>2.8144618093816121</v>
+        <v>2.8215079743062716</v>
       </c>
       <c r="Z107" s="17">
-        <v>19.163353614241402</v>
+        <v>19.482911734559821</v>
       </c>
       <c r="AA107" s="17"/>
       <c r="AB107" s="9"/>
@@ -11606,10 +11598,10 @@
         <v>-25.649717229370012</v>
       </c>
       <c r="Y108" s="17">
-        <v>23.460357363932289</v>
+        <v>23.479685109170802</v>
       </c>
       <c r="Z108" s="17">
-        <v>12.014846518911952</v>
+        <v>12.225687377283549</v>
       </c>
       <c r="AA108" s="17"/>
       <c r="AB108" s="9"/>
@@ -11751,10 +11743,10 @@
         <v>22.011318768929854</v>
       </c>
       <c r="Y109" s="17">
-        <v>-6.8475511466428856</v>
+        <v>-6.7833590528862402</v>
       </c>
       <c r="Z109" s="17">
-        <v>3.8039893388130253</v>
+        <v>4.2694930478868827</v>
       </c>
       <c r="AA109" s="17"/>
       <c r="AB109" s="9"/>
@@ -11896,10 +11888,10 @@
         <v>-1.7829205787171958</v>
       </c>
       <c r="Y110" s="17">
-        <v>45.355177965486007</v>
+        <v>45.141496566217057</v>
       </c>
       <c r="Z110" s="17">
-        <v>5.040717924897848</v>
+        <v>6.768030938175059</v>
       </c>
       <c r="AA110" s="17"/>
       <c r="AB110" s="9"/>
@@ -12041,10 +12033,10 @@
         <v>-7.9796421002632343</v>
       </c>
       <c r="Y111" s="17">
-        <v>11.9578636277339</v>
+        <v>11.990331115411095</v>
       </c>
       <c r="Z111" s="17">
-        <v>3.436940665998975</v>
+        <v>3.9712472072392302</v>
       </c>
       <c r="AA111" s="17"/>
       <c r="AB111" s="9"/>
@@ -12186,10 +12178,10 @@
         <v>20.673349298191141</v>
       </c>
       <c r="Y112" s="17">
-        <v>9.3577154557116415</v>
+        <v>9.3620386934331066</v>
       </c>
       <c r="Z112" s="17">
-        <v>17.473406879573346</v>
+        <v>17.460693125845978</v>
       </c>
       <c r="AA112" s="17"/>
       <c r="AB112" s="9"/>
@@ -12331,10 +12323,10 @@
         <v>18.931764740092461</v>
       </c>
       <c r="Y113" s="17">
-        <v>5.110855162531351</v>
+        <v>5.1786272577268875</v>
       </c>
       <c r="Z113" s="17">
-        <v>13.953019909154875</v>
+        <v>14.72756191479148</v>
       </c>
       <c r="AA113" s="17"/>
       <c r="AB113" s="9"/>
@@ -12476,10 +12468,10 @@
         <v>24.443269917302459</v>
       </c>
       <c r="Y114" s="17">
-        <v>5.4902544122010823</v>
+        <v>5.5397520385193104</v>
       </c>
       <c r="Z114" s="17">
-        <v>10.131913750062708</v>
+        <v>10.743288859219959</v>
       </c>
       <c r="AA114" s="17"/>
       <c r="AB114" s="9"/>
@@ -12621,10 +12613,10 @@
         <v>28.418441159952295</v>
       </c>
       <c r="Y115" s="17">
-        <v>-0.65270557536189244</v>
+        <v>-0.62351987097203221</v>
       </c>
       <c r="Z115" s="17">
-        <v>10.211535612552964</v>
+        <v>10.781724199013027</v>
       </c>
       <c r="AA115" s="17"/>
       <c r="AB115" s="9"/>
@@ -12766,10 +12758,10 @@
         <v>-11.503318450687559</v>
       </c>
       <c r="Y116" s="17">
-        <v>-1.238578427160391</v>
+        <v>-1.198495750264243</v>
       </c>
       <c r="Z116" s="17">
-        <v>-12.702348728338364</v>
+        <v>-12.65704945371273</v>
       </c>
       <c r="AA116" s="17"/>
       <c r="AB116" s="9"/>
@@ -12911,10 +12903,10 @@
         <v>-1.7254349921448409</v>
       </c>
       <c r="Y117" s="17">
-        <v>4.8104743910917449</v>
+        <v>4.8766975855916854</v>
       </c>
       <c r="Z117" s="17">
-        <v>10.933596681413377</v>
+        <v>11.995558334693129</v>
       </c>
       <c r="AA117" s="17"/>
       <c r="AB117" s="9"/>
@@ -13056,10 +13048,10 @@
         <v>29.877568319024562</v>
       </c>
       <c r="Y118" s="17">
-        <v>0.6549944559331351</v>
+        <v>0.94636368510812474</v>
       </c>
       <c r="Z118" s="17">
-        <v>3.368206422536062</v>
+        <v>4.5872213191508848</v>
       </c>
       <c r="AA118" s="17"/>
       <c r="AB118" s="9"/>
@@ -13201,10 +13193,10 @@
         <v>-7.2281698046945024</v>
       </c>
       <c r="Y119" s="17">
-        <v>16.611162285321228</v>
+        <v>16.8730564407565</v>
       </c>
       <c r="Z119" s="17">
-        <v>3.5758032109835369</v>
+        <v>3.8842246366979509</v>
       </c>
       <c r="AA119" s="17"/>
       <c r="AB119" s="9"/>
@@ -13346,10 +13338,10 @@
         <v>16.088452592187366</v>
       </c>
       <c r="Y120" s="17">
-        <v>-5.8286529500357886</v>
+        <v>-5.707125412988006</v>
       </c>
       <c r="Z120" s="17">
-        <v>11.516780304373725</v>
+        <v>12.702878271969297</v>
       </c>
       <c r="AA120" s="17"/>
       <c r="AB120" s="9"/>
@@ -13491,10 +13483,10 @@
         <v>-2.2136122204675246</v>
       </c>
       <c r="Y121" s="17">
-        <v>0.9880478566394828</v>
+        <v>1.0792937969342944</v>
       </c>
       <c r="Z121" s="17">
-        <v>0.64520057652133289</v>
+        <v>2.4286200928830937</v>
       </c>
       <c r="AA121" s="17"/>
       <c r="AB121" s="9"/>
@@ -13636,10 +13628,10 @@
         <v>4.0581275268477128</v>
       </c>
       <c r="Y122" s="17">
-        <v>0.18324901471125088</v>
+        <v>0.22403071027412125</v>
       </c>
       <c r="Z122" s="17">
-        <v>28.490983817899263</v>
+        <v>31.09665477114271</v>
       </c>
       <c r="AA122" s="17"/>
       <c r="AB122" s="9"/>
@@ -13781,10 +13773,10 @@
         <v>-9.4440237645164444</v>
       </c>
       <c r="Y123" s="17">
-        <v>5.1622648658038202</v>
+        <v>5.2543743327984487</v>
       </c>
       <c r="Z123" s="17">
-        <v>7.0576669426146736</v>
+        <v>7.7338111332826855</v>
       </c>
       <c r="AA123" s="17"/>
       <c r="AB123" s="9"/>
@@ -13926,10 +13918,10 @@
         <v>2.4807326149752811</v>
       </c>
       <c r="Y124" s="17">
-        <v>28.153492178084463</v>
+        <v>28.153542259394243</v>
       </c>
       <c r="Z124" s="17">
-        <v>-18.957252965289257</v>
+        <v>-18.575398560592532</v>
       </c>
       <c r="AA124" s="17"/>
       <c r="AB124" s="9"/>
@@ -14074,7 +14066,7 @@
         <v>7.5460482930225226</v>
       </c>
       <c r="Z125" s="17">
-        <v>10.668715254125871</v>
+        <v>11.097536245163212</v>
       </c>
       <c r="AA125" s="17"/>
       <c r="AB125" s="9"/>
@@ -14216,10 +14208,10 @@
         <v>-3.9361303896696569</v>
       </c>
       <c r="Y126" s="17">
-        <v>9.5027568657665142</v>
+        <v>9.5230747215599507</v>
       </c>
       <c r="Z126" s="17">
-        <v>1.9408173843218748</v>
+        <v>2.5426216294376758</v>
       </c>
       <c r="AA126" s="17"/>
       <c r="AB126" s="9"/>
@@ -14361,10 +14353,10 @@
         <v>-0.34484378074812128</v>
       </c>
       <c r="Y127" s="17">
-        <v>8.9145317839388412</v>
+        <v>8.9268274400024836</v>
       </c>
       <c r="Z127" s="17">
-        <v>-3.7872430690223808</v>
+        <v>-3.4111837220689836</v>
       </c>
       <c r="AA127" s="17"/>
       <c r="AB127" s="9"/>
@@ -14506,10 +14498,10 @@
         <v>-7.5888154612020742</v>
       </c>
       <c r="Y128" s="17">
-        <v>3.909093513519224E-2</v>
+        <v>4.7622226081102781E-2</v>
       </c>
       <c r="Z128" s="17">
-        <v>-16.832856599796997</v>
+        <v>-15.94733806879114</v>
       </c>
       <c r="AA128" s="17"/>
       <c r="AB128" s="9"/>
@@ -14651,10 +14643,10 @@
         <v>48.998411165856595</v>
       </c>
       <c r="Y129" s="17">
-        <v>5.0625689059820616</v>
+        <v>5.0675186748792385</v>
       </c>
       <c r="Z129" s="17">
-        <v>-78.999917334597598</v>
+        <v>-78.248283886103522</v>
       </c>
       <c r="AA129" s="17"/>
       <c r="AB129" s="9"/>
@@ -14796,10 +14788,10 @@
         <v>7.317422959836108</v>
       </c>
       <c r="Y130" s="17">
-        <v>10.425909218132361</v>
+        <v>10.579038157679705</v>
       </c>
       <c r="Z130" s="17">
-        <v>25.65205909035268</v>
+        <v>26.592311117794878</v>
       </c>
       <c r="AA130" s="17"/>
       <c r="AB130" s="9"/>
@@ -14941,10 +14933,10 @@
         <v>-13.222613977739073</v>
       </c>
       <c r="Y131" s="17">
-        <v>13.055026565534675</v>
+        <v>13.065407477583136</v>
       </c>
       <c r="Z131" s="17">
-        <v>5.8191955097927348</v>
+        <v>6.4738990173915454</v>
       </c>
       <c r="AA131" s="17"/>
       <c r="AB131" s="9"/>
@@ -15086,10 +15078,10 @@
         <v>12.689087773918018</v>
       </c>
       <c r="Y132" s="17">
-        <v>16.578261674549651</v>
+        <v>16.580305588634175</v>
       </c>
       <c r="Z132" s="17">
-        <v>18.277878228052785</v>
+        <v>18.76971330435353</v>
       </c>
       <c r="AA132" s="17"/>
       <c r="AB132" s="9"/>
@@ -15231,10 +15223,10 @@
         <v>0.28701882694075209</v>
       </c>
       <c r="Y133" s="17">
-        <v>-4.3389645073410321</v>
+        <v>-4.3008940251353351</v>
       </c>
       <c r="Z133" s="17">
-        <v>19.083729802767607</v>
+        <v>19.566364592164206</v>
       </c>
       <c r="AA133" s="17"/>
       <c r="AB133" s="9"/>
@@ -15376,10 +15368,10 @@
         <v>13.797112098373731</v>
       </c>
       <c r="Y134" s="17">
-        <v>8.5918595666974369</v>
+        <v>8.6079368888323273</v>
       </c>
       <c r="Z134" s="17">
-        <v>5.2378068995619884</v>
+        <v>5.4412994425579626</v>
       </c>
       <c r="AA134" s="17"/>
       <c r="AB134" s="9"/>
@@ -15521,10 +15513,10 @@
         <v>-1.8520666766931697</v>
       </c>
       <c r="Y135" s="17">
-        <v>3.6637608659148384</v>
+        <v>3.8186207234943765</v>
       </c>
       <c r="Z135" s="17">
-        <v>13.072951333709497</v>
+        <v>13.680109284499252</v>
       </c>
       <c r="AA135" s="17"/>
       <c r="AB135" s="9"/>
@@ -15758,10 +15750,10 @@
         <v>-3.3485673907349707</v>
       </c>
       <c r="Y137" s="17">
-        <v>4.6937952410344366</v>
+        <v>4.7763771971983431</v>
       </c>
       <c r="Z137" s="17">
-        <v>5.1063459845525045</v>
+        <v>5.7144389919627514</v>
       </c>
       <c r="AA137" s="17"/>
       <c r="AB137" s="9"/>
@@ -16060,7 +16052,7 @@
     </row>
     <row r="144" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="146" spans="1:91" x14ac:dyDescent="0.2">
@@ -16070,7 +16062,7 @@
     </row>
     <row r="147" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="148" spans="1:91" x14ac:dyDescent="0.2">
@@ -16186,7 +16178,7 @@
         <v>74</v>
       </c>
       <c r="Z151" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA151" s="16"/>
     </row>
@@ -16267,10 +16259,10 @@
         <v>-12.178550231748062</v>
       </c>
       <c r="Y153" s="17">
-        <v>7.2717166121126127</v>
+        <v>7.2745844871580516</v>
       </c>
       <c r="Z153" s="17">
-        <v>13.887985404766738</v>
+        <v>13.703014200420256</v>
       </c>
       <c r="AA153" s="17"/>
       <c r="AB153" s="9"/>
@@ -16412,10 +16404,10 @@
         <v>-13.013919616364248</v>
       </c>
       <c r="Y154" s="17">
-        <v>0.30638879435842625</v>
+        <v>0.31381202105855266</v>
       </c>
       <c r="Z154" s="17">
-        <v>19.261315803085253</v>
+        <v>18.621241832132654</v>
       </c>
       <c r="AA154" s="17"/>
       <c r="AB154" s="9"/>
@@ -16557,10 +16549,10 @@
         <v>-27.840257907942188</v>
       </c>
       <c r="Y155" s="17">
-        <v>23.607101067523487</v>
+        <v>23.626774730958203</v>
       </c>
       <c r="Z155" s="17">
-        <v>9.0486013825999976</v>
+        <v>8.9156515487216978</v>
       </c>
       <c r="AA155" s="17"/>
       <c r="AB155" s="9"/>
@@ -16702,10 +16694,10 @@
         <v>33.733220977279046</v>
       </c>
       <c r="Y156" s="17">
-        <v>-1.5915064598530648</v>
+        <v>-1.5151535389449435</v>
       </c>
       <c r="Z156" s="17">
-        <v>-1.8151262250827784</v>
+        <v>-1.6086560369767682</v>
       </c>
       <c r="AA156" s="17"/>
       <c r="AB156" s="9"/>
@@ -16847,10 +16839,10 @@
         <v>-10.677822413162446</v>
       </c>
       <c r="Y157" s="17">
-        <v>45.824833730461251</v>
+        <v>45.610596607202353</v>
       </c>
       <c r="Z157" s="17">
-        <v>4.8021296183948152</v>
+        <v>6.2959391223658798</v>
       </c>
       <c r="AA157" s="17"/>
       <c r="AB157" s="9"/>
@@ -16992,10 +16984,10 @@
         <v>-10.3635492151694</v>
       </c>
       <c r="Y158" s="17">
-        <v>5.4390890732798312</v>
+        <v>5.4720627432378564</v>
       </c>
       <c r="Z158" s="17">
-        <v>-1.6685827829126509</v>
+        <v>-1.3021553152490668</v>
       </c>
       <c r="AA158" s="17"/>
       <c r="AB158" s="9"/>
@@ -17137,10 +17129,10 @@
         <v>11.465122726428859</v>
       </c>
       <c r="Y159" s="17">
-        <v>3.8405663661836797</v>
+        <v>3.8455450403767912</v>
       </c>
       <c r="Z159" s="17">
-        <v>25.773792472313417</v>
+        <v>25.754888716138666</v>
       </c>
       <c r="AA159" s="17"/>
       <c r="AB159" s="9"/>
@@ -17282,10 +17274,10 @@
         <v>8.0764320281995623</v>
       </c>
       <c r="Y160" s="17">
-        <v>5.0997596659518649</v>
+        <v>5.1487025764615595</v>
       </c>
       <c r="Z160" s="17">
-        <v>0.29999745359671692</v>
+        <v>0.69650355148567655</v>
       </c>
       <c r="AA160" s="17"/>
       <c r="AB160" s="9"/>
@@ -17427,10 +17419,10 @@
         <v>20.972899909310485</v>
       </c>
       <c r="Y161" s="17">
-        <v>-6.202086944043117E-2</v>
+        <v>-1.5324253276389754E-2</v>
       </c>
       <c r="Z161" s="17">
-        <v>-0.41642232227664522</v>
+        <v>0.34623836999259083</v>
       </c>
       <c r="AA161" s="17"/>
       <c r="AB161" s="9"/>
@@ -17572,10 +17564,10 @@
         <v>19.035204430508415</v>
       </c>
       <c r="Y162" s="17">
-        <v>-8.7261097710813118</v>
+        <v>-8.702140379262687</v>
       </c>
       <c r="Z162" s="17">
-        <v>5.844261392441652</v>
+        <v>6.2675452445004822</v>
       </c>
       <c r="AA162" s="17"/>
       <c r="AB162" s="9"/>
@@ -17717,10 +17709,10 @@
         <v>-6.9970682028325939</v>
       </c>
       <c r="Y163" s="17">
-        <v>0.46157231482285965</v>
+        <v>0.49136216013592104</v>
       </c>
       <c r="Z163" s="17">
-        <v>-1.6840917529017219</v>
+        <v>-2.5802985672836627</v>
       </c>
       <c r="AA163" s="17"/>
       <c r="AB163" s="9"/>
@@ -17862,10 +17854,10 @@
         <v>-8.3762736961583215</v>
       </c>
       <c r="Y164" s="17">
-        <v>-0.52468401182939317</v>
+        <v>-0.46167846893987985</v>
       </c>
       <c r="Z164" s="17">
-        <v>5.811871167354667</v>
+        <v>6.8241231222730789</v>
       </c>
       <c r="AA164" s="17"/>
       <c r="AB164" s="9"/>
@@ -18007,10 +17999,10 @@
         <v>22.752130190229636</v>
       </c>
       <c r="Y165" s="17">
-        <v>8.4577599270677268</v>
+        <v>8.7366066800559139</v>
       </c>
       <c r="Z165" s="17">
-        <v>-9.6355597263276707</v>
+        <v>-8.3809235928468411</v>
       </c>
       <c r="AA165" s="17"/>
       <c r="AB165" s="9"/>
@@ -18152,10 +18144,10 @@
         <v>-1.3693128401278472</v>
       </c>
       <c r="Y166" s="17">
-        <v>6.1184326555741393</v>
+        <v>6.3745907240663655</v>
       </c>
       <c r="Z166" s="17">
-        <v>-7.9664183303856504</v>
+        <v>-7.8022897196860299</v>
       </c>
       <c r="AA166" s="17"/>
       <c r="AB166" s="9"/>
@@ -18297,10 +18289,10 @@
         <v>3.4866039955399941</v>
       </c>
       <c r="Y167" s="17">
-        <v>-14.45792077682367</v>
+        <v>-14.345359450550347</v>
       </c>
       <c r="Z167" s="17">
-        <v>8.8593196953363957</v>
+        <v>9.92531779620127</v>
       </c>
       <c r="AA167" s="17"/>
       <c r="AB167" s="9"/>
@@ -18442,10 +18434,10 @@
         <v>-4.8371081733348547</v>
       </c>
       <c r="Y168" s="17">
-        <v>0.5140095200464998</v>
+        <v>0.58011325980631057</v>
       </c>
       <c r="Z168" s="17">
-        <v>-2.6357396451443265</v>
+        <v>-1.1241773379697122</v>
       </c>
       <c r="AA168" s="17"/>
       <c r="AB168" s="9"/>
@@ -18587,10 +18579,10 @@
         <v>-2.0075327213091043</v>
       </c>
       <c r="Y169" s="17">
-        <v>-3.1485170295203488</v>
+        <v>-3.1065334157571556</v>
       </c>
       <c r="Z169" s="17">
-        <v>25.976684773218466</v>
+        <v>28.574189362859983</v>
       </c>
       <c r="AA169" s="17"/>
       <c r="AB169" s="9"/>
@@ -18732,10 +18724,10 @@
         <v>-5.7124576485500853</v>
       </c>
       <c r="Y170" s="17">
-        <v>1.7556263210234135</v>
+        <v>1.8439441281622493</v>
       </c>
       <c r="Z170" s="17">
-        <v>3.861644975438665</v>
+        <v>4.5732175647927136</v>
       </c>
       <c r="AA170" s="17"/>
       <c r="AB170" s="9"/>
@@ -18877,10 +18869,10 @@
         <v>-6.7191257640067192</v>
       </c>
       <c r="Y171" s="17">
-        <v>29.044637319961794</v>
+        <v>29.044716558486186</v>
       </c>
       <c r="Z171" s="17">
-        <v>-2.2731254756521935</v>
+        <v>-2.0030474578463782</v>
       </c>
       <c r="AA171" s="17"/>
       <c r="AB171" s="9"/>
@@ -19025,7 +19017,7 @@
         <v>1.8447220590395403</v>
       </c>
       <c r="Z172" s="17">
-        <v>0.20247909770900208</v>
+        <v>0.48352126594370759</v>
       </c>
       <c r="AA172" s="17"/>
       <c r="AB172" s="9"/>
@@ -19167,10 +19159,10 @@
         <v>-5.3290613525504398</v>
       </c>
       <c r="Y173" s="17">
-        <v>9.0049876559930482</v>
+        <v>9.025589591113345</v>
       </c>
       <c r="Z173" s="17">
-        <v>-4.5911944365915218</v>
+        <v>-4.0749202206672663</v>
       </c>
       <c r="AA173" s="17"/>
       <c r="AB173" s="9"/>
@@ -19312,10 +19304,10 @@
         <v>5.741102613153771</v>
       </c>
       <c r="Y174" s="17">
-        <v>5.7424249828946756</v>
+        <v>5.7561800531902776</v>
       </c>
       <c r="Z174" s="17">
-        <v>-5.0540358484922621</v>
+        <v>-5.4890372895059159</v>
       </c>
       <c r="AA174" s="17"/>
       <c r="AB174" s="9"/>
@@ -19457,10 +19449,10 @@
         <v>-1.6548604539794667</v>
       </c>
       <c r="Y175" s="17">
-        <v>19.2681428735048</v>
+        <v>19.279720709973375</v>
       </c>
       <c r="Z175" s="17">
-        <v>-18.287001460535507</v>
+        <v>-17.584061616213077</v>
       </c>
       <c r="AA175" s="17"/>
       <c r="AB175" s="9"/>
@@ -19602,10 +19594,10 @@
         <v>92.251230925038385</v>
       </c>
       <c r="Y176" s="17">
-        <v>-10.721178204001248</v>
+        <v>-10.718469167660558</v>
       </c>
       <c r="Z176" s="17">
-        <v>-67.444361337978179</v>
+        <v>-66.850308011162937</v>
       </c>
       <c r="AA176" s="17"/>
       <c r="AB176" s="9"/>
@@ -19747,10 +19739,10 @@
         <v>12.948890457188583</v>
       </c>
       <c r="Y177" s="17">
-        <v>4.207195334911404</v>
+        <v>4.2899896108782798</v>
       </c>
       <c r="Z177" s="17">
-        <v>16.775226246572373</v>
+        <v>17.774085121138498</v>
       </c>
       <c r="AA177" s="17"/>
       <c r="AB177" s="9"/>
@@ -19892,10 +19884,10 @@
         <v>-3.9646701964432083</v>
       </c>
       <c r="Y178" s="17">
-        <v>7.7972815214044431</v>
+        <v>7.8076148486575079</v>
       </c>
       <c r="Z178" s="17">
-        <v>6.8034799789810734</v>
+        <v>7.8162978129822989</v>
       </c>
       <c r="AA178" s="17"/>
       <c r="AB178" s="9"/>
@@ -20037,10 +20029,10 @@
         <v>1.8785316662388141E-2</v>
       </c>
       <c r="Y179" s="17">
-        <v>2.1676850188122216</v>
+        <v>2.1696357569429949</v>
       </c>
       <c r="Z179" s="17">
-        <v>11.435576762837528</v>
+        <v>11.742028197395584</v>
       </c>
       <c r="AA179" s="17"/>
       <c r="AB179" s="9"/>
@@ -20182,10 +20174,10 @@
         <v>-1.7941301856229188</v>
       </c>
       <c r="Y180" s="17">
-        <v>-8.2925531061443962</v>
+        <v>-8.2528960702338452</v>
       </c>
       <c r="Z180" s="17">
-        <v>15.715220370448876</v>
+        <v>16.193139222876908</v>
       </c>
       <c r="AA180" s="17"/>
       <c r="AB180" s="9"/>
@@ -20327,10 +20319,10 @@
         <v>72.233937578457983</v>
       </c>
       <c r="Y181" s="17">
-        <v>2.6971117279093022</v>
+        <v>2.7119005859913585</v>
       </c>
       <c r="Z181" s="17">
-        <v>4.1539192446359721</v>
+        <v>4.1827424235459318</v>
       </c>
       <c r="AA181" s="17"/>
       <c r="AB181" s="9"/>
@@ -20472,10 +20464,10 @@
         <v>-5.6230852822508695</v>
       </c>
       <c r="Y182" s="17">
-        <v>1.687204193579845</v>
+        <v>2.0806572395551655</v>
       </c>
       <c r="Z182" s="17">
-        <v>5.8869024682071824</v>
+        <v>4.7751537776286312</v>
       </c>
       <c r="AA182" s="17"/>
       <c r="AB182" s="9"/>
@@ -20709,10 +20701,10 @@
         <v>-4.582507461526049</v>
       </c>
       <c r="Y184" s="17">
-        <v>1.8479769930565624</v>
+        <v>1.9705915387760626</v>
       </c>
       <c r="Z184" s="17">
-        <v>4.7309627500855527</v>
+        <v>4.7093734316453464</v>
       </c>
       <c r="AA184" s="17"/>
       <c r="AB184" s="9"/>
@@ -21006,7 +20998,7 @@
     </row>
     <row r="190" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="192" spans="1:92" x14ac:dyDescent="0.2">
@@ -21016,7 +21008,7 @@
     </row>
     <row r="193" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="194" spans="1:96" x14ac:dyDescent="0.2">
@@ -21218,10 +21210,10 @@
         <v>106.73435631182751</v>
       </c>
       <c r="Z199" s="17">
-        <v>109.13645623738265</v>
+        <v>109.13630536310603</v>
       </c>
       <c r="AA199" s="17">
-        <v>110.0945323921613</v>
+        <v>110.68623589234367</v>
       </c>
       <c r="AB199" s="9"/>
       <c r="AC199" s="9"/>
@@ -21370,10 +21362,10 @@
         <v>105.44343456390486</v>
       </c>
       <c r="Z200" s="17">
-        <v>108.07995488947724</v>
+        <v>108.0793634437378</v>
       </c>
       <c r="AA200" s="17">
-        <v>107.99117715899673</v>
+        <v>108.86445667927104</v>
       </c>
       <c r="AB200" s="9"/>
       <c r="AC200" s="9"/>
@@ -21522,10 +21514,10 @@
         <v>101.96730976926402</v>
       </c>
       <c r="Z201" s="17">
-        <v>101.84625636252973</v>
+        <v>101.8459903134966</v>
       </c>
       <c r="AA201" s="17">
-        <v>104.61658957869824</v>
+        <v>104.94117334862023</v>
       </c>
       <c r="AB201" s="9"/>
       <c r="AC201" s="9"/>
@@ -21674,10 +21666,10 @@
         <v>107.92102337354214</v>
       </c>
       <c r="Z202" s="17">
-        <v>102.15690992063156</v>
+        <v>102.14805270001308</v>
       </c>
       <c r="AA202" s="17">
-        <v>108.00334492049164</v>
+        <v>108.25063711765088</v>
       </c>
       <c r="AB202" s="9"/>
       <c r="AC202" s="9"/>
@@ -21826,10 +21818,10 @@
         <v>116.14943810390834</v>
       </c>
       <c r="Z203" s="17">
-        <v>115.77535742225322</v>
+        <v>115.77525032194393</v>
       </c>
       <c r="AA203" s="17">
-        <v>116.0389269371356</v>
+        <v>116.28944257238665</v>
       </c>
       <c r="AB203" s="9"/>
       <c r="AC203" s="9"/>
@@ -21978,10 +21970,10 @@
         <v>111.72270097262853</v>
       </c>
       <c r="Z204" s="17">
-        <v>118.62996000394554</v>
+        <v>118.62726441116185</v>
       </c>
       <c r="AA204" s="17">
-        <v>124.78941605252922</v>
+        <v>124.96549112097325</v>
       </c>
       <c r="AB204" s="9"/>
       <c r="AC204" s="9"/>
@@ -22130,10 +22122,10 @@
         <v>105.6605355497227</v>
       </c>
       <c r="Z205" s="17">
-        <v>111.27438135109755</v>
+        <v>111.2734453140457</v>
       </c>
       <c r="AA205" s="17">
-        <v>103.93087795780495</v>
+        <v>103.93437699739592</v>
       </c>
       <c r="AB205" s="9"/>
       <c r="AC205" s="9"/>
@@ -22282,10 +22274,10 @@
         <v>118.38063007468421</v>
       </c>
       <c r="Z206" s="17">
-        <v>118.39312764727853</v>
+        <v>118.41432048204229</v>
       </c>
       <c r="AA206" s="17">
-        <v>134.50902068207034</v>
+        <v>134.91418078637975</v>
       </c>
       <c r="AB206" s="9"/>
       <c r="AC206" s="9"/>
@@ -22434,10 +22426,10 @@
         <v>108.73024508211331</v>
       </c>
       <c r="Z207" s="17">
-        <v>114.77099412855505</v>
+        <v>114.77121888280672</v>
       </c>
       <c r="AA207" s="17">
-        <v>126.9280489929868</v>
+        <v>126.66286700851811</v>
       </c>
       <c r="AB207" s="9"/>
       <c r="AC207" s="9"/>
@@ -22586,10 +22578,10 @@
         <v>116.56257076757939</v>
       </c>
       <c r="Z208" s="17">
-        <v>126.8728220950796</v>
+        <v>126.87677505028481</v>
       </c>
       <c r="AA208" s="17">
-        <v>132.10776254323676</v>
+        <v>132.26642121582523</v>
       </c>
       <c r="AB208" s="9"/>
       <c r="AC208" s="9"/>
@@ -22738,10 +22730,10 @@
         <v>149.75612692189429</v>
       </c>
       <c r="Z209" s="17">
-        <v>147.22174502405858</v>
+        <v>147.23783509790061</v>
       </c>
       <c r="AA209" s="17">
-        <v>130.72261433433968</v>
+        <v>132.00807188246537</v>
       </c>
       <c r="AB209" s="9"/>
       <c r="AC209" s="9"/>
@@ -22890,10 +22882,10 @@
         <v>118.70090800741384</v>
       </c>
       <c r="Z210" s="17">
-        <v>125.06719235141566</v>
+        <v>125.06699973179761</v>
       </c>
       <c r="AA210" s="17">
-        <v>131.12095383366756</v>
+        <v>131.12158616247143</v>
       </c>
       <c r="AB210" s="9"/>
       <c r="AC210" s="9"/>
@@ -23042,10 +23034,10 @@
         <v>123.10023194722206</v>
       </c>
       <c r="Z211" s="17">
-        <v>114.24404461703614</v>
+        <v>114.28093227544751</v>
       </c>
       <c r="AA211" s="17">
-        <v>130.68417123765244</v>
+        <v>130.45673046664706</v>
       </c>
       <c r="AB211" s="9"/>
       <c r="AC211" s="9"/>
@@ -23194,10 +23186,10 @@
         <v>139.48277612074159</v>
       </c>
       <c r="Z212" s="17">
-        <v>153.27448997493792</v>
+        <v>153.24879987890463</v>
       </c>
       <c r="AA212" s="17">
-        <v>172.49712684114172</v>
+        <v>172.67384085268071</v>
       </c>
       <c r="AB212" s="9"/>
       <c r="AC212" s="9"/>
@@ -23346,10 +23338,10 @@
         <v>123.90335737273503</v>
       </c>
       <c r="Z213" s="17">
-        <v>136.40241356960453</v>
+        <v>136.39895822004124</v>
       </c>
       <c r="AA213" s="17">
-        <v>139.73225287094616</v>
+        <v>139.84544682597195</v>
       </c>
       <c r="AB213" s="9"/>
       <c r="AC213" s="9"/>
@@ -23498,10 +23490,10 @@
         <v>103.77610115638105</v>
       </c>
       <c r="Z214" s="17">
-        <v>104.26552398017623</v>
+        <v>104.29114342703826</v>
       </c>
       <c r="AA214" s="17">
-        <v>107.77902010403955</v>
+        <v>108.03852369101628</v>
       </c>
       <c r="AB214" s="9"/>
       <c r="AC214" s="9"/>
@@ -23650,10 +23642,10 @@
         <v>122.65065001923394</v>
       </c>
       <c r="Z215" s="17">
-        <v>126.86992739634518</v>
+        <v>126.86657777359207</v>
       </c>
       <c r="AA215" s="17">
-        <v>129.40205417699184</v>
+        <v>129.35554196995929</v>
       </c>
       <c r="AB215" s="9"/>
       <c r="AC215" s="9"/>
@@ -23802,10 +23794,10 @@
         <v>117.81112996125158</v>
       </c>
       <c r="Z216" s="17">
-        <v>121.75528470571717</v>
+        <v>121.75625050328949</v>
       </c>
       <c r="AA216" s="17">
-        <v>125.5019282778584</v>
+        <v>125.43617956376538</v>
       </c>
       <c r="AB216" s="9"/>
       <c r="AC216" s="9"/>
@@ -23954,10 +23946,10 @@
         <v>178.69935226198774</v>
       </c>
       <c r="Z217" s="17">
-        <v>177.46530594334803</v>
+        <v>177.46526632459029</v>
       </c>
       <c r="AA217" s="17">
-        <v>147.16807395105101</v>
+        <v>147.45395856674571</v>
       </c>
       <c r="AB217" s="9"/>
       <c r="AC217" s="9"/>
@@ -24109,7 +24101,7 @@
         <v>163.01644448598398</v>
       </c>
       <c r="AA218" s="17">
-        <v>180.04365399949327</v>
+        <v>180.23577519647895</v>
       </c>
       <c r="AB218" s="9"/>
       <c r="AC218" s="9"/>
@@ -24258,10 +24250,10 @@
         <v>116.57490463593876</v>
       </c>
       <c r="Z219" s="17">
-        <v>117.1072417281017</v>
+        <v>117.10683738546217</v>
       </c>
       <c r="AA219" s="17">
-        <v>125.12480240046695</v>
+        <v>125.18563595528829</v>
       </c>
       <c r="AB219" s="9"/>
       <c r="AC219" s="9"/>
@@ -24410,10 +24402,10 @@
         <v>125.36742846377915</v>
       </c>
       <c r="Z220" s="17">
-        <v>129.12825457045963</v>
+        <v>129.12603537687045</v>
       </c>
       <c r="AA220" s="17">
-        <v>130.85111601040856</v>
+        <v>131.96491232365054</v>
       </c>
       <c r="AB220" s="9"/>
       <c r="AC220" s="9"/>
@@ -24562,10 +24554,10 @@
         <v>170.33446702849432</v>
       </c>
       <c r="Z221" s="17">
-        <v>142.8722274524219</v>
+        <v>142.87054251899136</v>
       </c>
       <c r="AA221" s="17">
-        <v>145.41474723514489</v>
+        <v>145.707852701457</v>
       </c>
       <c r="AB221" s="9"/>
       <c r="AC221" s="9"/>
@@ -24714,10 +24706,10 @@
         <v>146.22795047385733</v>
       </c>
       <c r="Z222" s="17">
-        <v>172.07982602799876</v>
+        <v>172.08271155265928</v>
       </c>
       <c r="AA222" s="17">
-        <v>111.00045092500777</v>
+        <v>112.91490403782454</v>
       </c>
       <c r="AB222" s="9"/>
       <c r="AC222" s="9"/>
@@ -24866,10 +24858,10 @@
         <v>129.89655578006713</v>
       </c>
       <c r="Z223" s="17">
-        <v>137.64831910328039</v>
+        <v>137.72976919212343</v>
       </c>
       <c r="AA223" s="17">
-        <v>148.11184941858147</v>
+        <v>148.04215862783195</v>
       </c>
       <c r="AB223" s="9"/>
       <c r="AC223" s="9"/>
@@ -25018,10 +25010,10 @@
         <v>109.74961176919899</v>
       </c>
       <c r="Z224" s="17">
-        <v>115.10258050116231</v>
+        <v>115.10211586269561</v>
       </c>
       <c r="AA224" s="17">
-        <v>114.04181279609227</v>
+        <v>113.66900282841161</v>
       </c>
       <c r="AB224" s="9"/>
       <c r="AC224" s="9"/>
@@ -25170,10 +25162,10 @@
         <v>143.27950876875525</v>
       </c>
       <c r="Z225" s="17">
-        <v>163.48883761797376</v>
+        <v>163.48858242568198</v>
       </c>
       <c r="AA225" s="17">
-        <v>173.52728266107289</v>
+        <v>173.77071435406427</v>
       </c>
       <c r="AB225" s="9"/>
       <c r="AC225" s="9"/>
@@ -25322,10 +25314,10 @@
         <v>104.15509768245204</v>
       </c>
       <c r="Z226" s="17">
-        <v>108.64531544177103</v>
+        <v>108.641573455721</v>
       </c>
       <c r="AA226" s="17">
-        <v>111.80801753637215</v>
+        <v>111.79556786701903</v>
       </c>
       <c r="AB226" s="9"/>
       <c r="AC226" s="9"/>
@@ -25474,10 +25466,10 @@
         <v>79.460760558408978</v>
       </c>
       <c r="Z227" s="17">
-        <v>84.021756858004508</v>
+        <v>84.022096939401152</v>
       </c>
       <c r="AA227" s="17">
-        <v>84.896137252559626</v>
+        <v>85.037107654182392</v>
       </c>
       <c r="AB227" s="9"/>
       <c r="AC227" s="9"/>
@@ -25626,10 +25618,10 @@
         <v>138.57273142455682</v>
       </c>
       <c r="Z228" s="17">
-        <v>141.2662547549798</v>
+        <v>140.93198687606144</v>
       </c>
       <c r="AA228" s="17">
-        <v>150.85333480031952</v>
+        <v>152.90995137792947</v>
       </c>
       <c r="AB228" s="9"/>
       <c r="AC228" s="9"/>
@@ -25875,10 +25867,10 @@
         <v>128.88446611195562</v>
       </c>
       <c r="Z230" s="17">
-        <v>132.48573318049347</v>
+        <v>132.43080414092378</v>
       </c>
       <c r="AA230" s="17">
-        <v>132.96059679041454</v>
+        <v>133.70195720014891</v>
       </c>
       <c r="AB230" s="9"/>
       <c r="AC230" s="9"/>
@@ -25999,7 +25991,7 @@
     </row>
     <row r="237" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="239" spans="1:96" x14ac:dyDescent="0.2">
@@ -26009,7 +26001,7 @@
     </row>
     <row r="240" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:96" x14ac:dyDescent="0.2">
@@ -26211,10 +26203,10 @@
         <v>15.162253794286082</v>
       </c>
       <c r="Z246" s="17">
-        <v>15.885235624420929</v>
+        <v>15.87311771219122</v>
       </c>
       <c r="AA246" s="17">
-        <v>17.36355060375416</v>
+        <v>17.315070993298935</v>
       </c>
       <c r="AB246" s="9"/>
       <c r="AC246" s="9"/>
@@ -26363,10 +26355,10 @@
         <v>8.2029520841044068</v>
       </c>
       <c r="Z247" s="17">
-        <v>8.0557028411630114</v>
+        <v>8.0499051951487637</v>
       </c>
       <c r="AA247" s="17">
-        <v>9.1330790475185992</v>
+        <v>9.0983419206969458</v>
       </c>
       <c r="AB247" s="9"/>
       <c r="AC247" s="9"/>
@@ -26515,10 +26507,10 @@
         <v>2.2804101277751183</v>
       </c>
       <c r="Z248" s="17">
-        <v>2.6891779848391404</v>
+        <v>2.6874791057861174</v>
       </c>
       <c r="AA248" s="17">
-        <v>2.8659340824013122</v>
+        <v>2.8530084710742751</v>
       </c>
       <c r="AB248" s="9"/>
       <c r="AC248" s="9"/>
@@ -26667,10 +26659,10 @@
         <v>0.18486134847775226</v>
       </c>
       <c r="Z249" s="17">
-        <v>0.16448240575662118</v>
+        <v>0.16446602189363238</v>
       </c>
       <c r="AA249" s="17">
-        <v>0.16244432944222018</v>
+        <v>0.16221803653288552</v>
       </c>
       <c r="AB249" s="9"/>
       <c r="AC249" s="9"/>
@@ -26819,10 +26811,10 @@
         <v>0.87690305786015299</v>
       </c>
       <c r="Z250" s="17">
-        <v>1.217478072509333</v>
+        <v>1.2147301287366696</v>
       </c>
       <c r="AA250" s="17">
-        <v>1.216717883171359</v>
+        <v>1.2268366100523933</v>
       </c>
       <c r="AB250" s="9"/>
       <c r="AC250" s="9"/>
@@ -26971,10 +26963,10 @@
         <v>1.1657082822160281</v>
       </c>
       <c r="Z251" s="17">
-        <v>1.246589719950365</v>
+        <v>1.2459684138882483</v>
       </c>
       <c r="AA251" s="17">
-        <v>1.2267901208962306</v>
+        <v>1.2254228581077353</v>
       </c>
       <c r="AB251" s="9"/>
       <c r="AC251" s="9"/>
@@ -27123,10 +27115,10 @@
         <v>1.2948218207285922</v>
       </c>
       <c r="Z252" s="17">
-        <v>1.3525038032204664</v>
+        <v>1.351491222044354</v>
       </c>
       <c r="AA252" s="17">
-        <v>1.5116425948747123</v>
+        <v>1.5016595387399789</v>
       </c>
       <c r="AB252" s="9"/>
       <c r="AC252" s="9"/>
@@ -27275,10 +27267,10 @@
         <v>0.8815263566098267</v>
       </c>
       <c r="Z253" s="17">
-        <v>0.88503801947617633</v>
+        <v>0.88491065028163818</v>
       </c>
       <c r="AA253" s="17">
-        <v>0.95953059835749677</v>
+        <v>0.96035737773686392</v>
       </c>
       <c r="AB253" s="9"/>
       <c r="AC253" s="9"/>
@@ -27427,10 +27419,10 @@
         <v>0.22563708897740112</v>
       </c>
       <c r="Z254" s="17">
-        <v>0.22735362555397326</v>
+        <v>0.22728102515463758</v>
       </c>
       <c r="AA254" s="17">
-        <v>0.23822433979347174</v>
+        <v>0.23809281363005938</v>
       </c>
       <c r="AB254" s="9"/>
       <c r="AC254" s="9"/>
@@ -27579,10 +27571,10 @@
         <v>4.9433627536803325E-2</v>
       </c>
       <c r="Z255" s="17">
-        <v>4.690915195184181E-2</v>
+        <v>4.6885949257160074E-2</v>
       </c>
       <c r="AA255" s="17">
-        <v>4.9187607298753377E-2</v>
+        <v>4.9133366727798868E-2</v>
       </c>
       <c r="AB255" s="9"/>
       <c r="AC255" s="9"/>
@@ -27731,10 +27723,10 @@
         <v>18.092712243845995</v>
       </c>
       <c r="Z256" s="17">
-        <v>17.06750602742688</v>
+        <v>17.060975321614716</v>
       </c>
       <c r="AA256" s="17">
-        <v>14.175672984372165</v>
+        <v>14.096049111139063</v>
       </c>
       <c r="AB256" s="9"/>
       <c r="AC256" s="9"/>
@@ -27883,10 +27875,10 @@
         <v>4.4640628078565312</v>
       </c>
       <c r="Z257" s="17">
-        <v>4.4690379169642291</v>
+        <v>4.4683370204860964</v>
       </c>
       <c r="AA257" s="17">
-        <v>4.7168079642623706</v>
+        <v>4.7338273201730408</v>
       </c>
       <c r="AB257" s="9"/>
       <c r="AC257" s="9"/>
@@ -28035,10 +28027,10 @@
         <v>1.1250147474640244</v>
       </c>
       <c r="Z258" s="17">
-        <v>1.0816147500253286</v>
+        <v>1.0838907670463926</v>
       </c>
       <c r="AA258" s="17">
-        <v>1.06372812890584</v>
+        <v>1.0723333975927722</v>
       </c>
       <c r="AB258" s="9"/>
       <c r="AC258" s="9"/>
@@ -28187,10 +28179,10 @@
         <v>5.0164261128292447</v>
       </c>
       <c r="Z259" s="17">
-        <v>5.5874493630562005</v>
+        <v>5.5955843091629038</v>
       </c>
       <c r="AA259" s="17">
-        <v>5.5060857673075194</v>
+        <v>5.4987090021908545</v>
       </c>
       <c r="AB259" s="9"/>
       <c r="AC259" s="9"/>
@@ -28339,10 +28331,10 @@
         <v>10.051865952602675</v>
       </c>
       <c r="Z260" s="17">
-        <v>9.0415841258112053</v>
+        <v>9.0461167010035179</v>
       </c>
       <c r="AA260" s="17">
-        <v>9.5930301935316979</v>
+        <v>9.6441261866294354</v>
       </c>
       <c r="AB260" s="9"/>
       <c r="AC260" s="9"/>
@@ -28491,10 +28483,10 @@
         <v>0.94776209072352169</v>
       </c>
       <c r="Z261" s="17">
-        <v>0.91421505118176649</v>
+        <v>0.91431986274479771</v>
       </c>
       <c r="AA261" s="17">
-        <v>0.87541200613887316</v>
+        <v>0.88590094936401353</v>
       </c>
       <c r="AB261" s="9"/>
       <c r="AC261" s="9"/>
@@ -28643,10 +28635,10 @@
         <v>2.6618785880416129</v>
       </c>
       <c r="Z262" s="17">
-        <v>2.5471962767109444</v>
+        <v>2.5462247167869956</v>
       </c>
       <c r="AA262" s="17">
-        <v>3.113910511359431</v>
+        <v>3.1575775821101755</v>
       </c>
       <c r="AB262" s="9"/>
       <c r="AC262" s="9"/>
@@ -28795,10 +28787,10 @@
         <v>4.3031321644933378</v>
       </c>
       <c r="Z263" s="17">
-        <v>4.3223872378794157</v>
+        <v>4.3227633533524941</v>
       </c>
       <c r="AA263" s="17">
-        <v>4.4026332470725631</v>
+        <v>4.4053373893358128</v>
       </c>
       <c r="AB263" s="9"/>
       <c r="AC263" s="9"/>
@@ -28947,10 +28939,10 @@
         <v>3.0724241206722733</v>
       </c>
       <c r="Z264" s="17">
-        <v>3.7608903145580701</v>
+        <v>3.7579275493205806</v>
       </c>
       <c r="AA264" s="17">
-        <v>2.8998523308270925</v>
+        <v>2.8944745472741062</v>
       </c>
       <c r="AB264" s="9"/>
       <c r="AC264" s="9"/>
@@ -29099,10 +29091,10 @@
         <v>1.0116295410880798</v>
       </c>
       <c r="Z265" s="17">
-        <v>1.0391901375819477</v>
+        <v>1.0383710755310978</v>
       </c>
       <c r="AA265" s="17">
-        <v>1.0941854780857367</v>
+        <v>1.0912460899358873</v>
       </c>
       <c r="AB265" s="9"/>
       <c r="AC265" s="9"/>
@@ -29251,10 +29243,10 @@
         <v>2.3754889148400347</v>
       </c>
       <c r="Z266" s="17">
-        <v>2.4846036432261989</v>
+        <v>2.4831059908723332</v>
       </c>
       <c r="AA266" s="17">
-        <v>2.4097738713490027</v>
+        <v>2.4086037869166588</v>
       </c>
       <c r="AB266" s="9"/>
       <c r="AC266" s="9"/>
@@ -29403,10 +29395,10 @@
         <v>1.0235446152099781</v>
       </c>
       <c r="Z267" s="17">
-        <v>1.0648088768671631</v>
+        <v>1.0640897372151386</v>
       </c>
       <c r="AA267" s="17">
-        <v>0.97470991583157551</v>
+        <v>0.97223396454782285</v>
       </c>
       <c r="AB267" s="9"/>
       <c r="AC267" s="9"/>
@@ -29555,10 +29547,10 @@
         <v>1.5064673463065921</v>
       </c>
       <c r="Z268" s="17">
-        <v>1.4394895466441961</v>
+        <v>1.4384776415350133</v>
       </c>
       <c r="AA268" s="17">
-        <v>1.1390200318299151</v>
+        <v>1.1437214826324478</v>
       </c>
       <c r="AB268" s="9"/>
       <c r="AC268" s="9"/>
@@ -29707,10 +29699,10 @@
         <v>1.1366145668916077</v>
       </c>
       <c r="Z269" s="17">
-        <v>1.1406181806540132</v>
+        <v>1.1397728708281492</v>
       </c>
       <c r="AA269" s="17">
-        <v>0.22789371906160225</v>
+        <v>0.23451872948462207</v>
       </c>
       <c r="AB269" s="9"/>
       <c r="AC269" s="9"/>
@@ -29859,10 +29851,10 @@
         <v>1.8498683466853079</v>
       </c>
       <c r="Z270" s="17">
-        <v>1.9511509124898359</v>
+        <v>1.9523166191345298</v>
       </c>
       <c r="AA270" s="17">
-        <v>2.3325530675987971</v>
+        <v>2.3378856777427544</v>
       </c>
       <c r="AB270" s="9"/>
       <c r="AC270" s="9"/>
@@ -30011,10 +30003,10 @@
         <v>1.9997069768244642</v>
       </c>
       <c r="Z271" s="17">
-        <v>2.1594109265757573</v>
+        <v>2.1579070609101914</v>
       </c>
       <c r="AA271" s="17">
-        <v>2.1740564271817275</v>
+        <v>2.1734096182427467</v>
       </c>
       <c r="AB271" s="9"/>
       <c r="AC271" s="9"/>
@@ -30163,10 +30155,10 @@
         <v>1.1204287812427696</v>
       </c>
       <c r="Z272" s="17">
-        <v>1.2476158624940277</v>
+        <v>1.2466543814713582</v>
       </c>
       <c r="AA272" s="17">
-        <v>1.4039623932996717</v>
+        <v>1.4006107858948809</v>
       </c>
       <c r="AB272" s="9"/>
       <c r="AC272" s="9"/>
@@ -30315,10 +30307,10 @@
         <v>1.1199889989507246</v>
       </c>
       <c r="Z273" s="17">
-        <v>1.0233587113099507</v>
+        <v>1.0229590750169013</v>
       </c>
       <c r="AA273" s="17">
-        <v>1.1594482819034846</v>
+        <v>1.1569989766074715</v>
       </c>
       <c r="AB273" s="9"/>
       <c r="AC273" s="9"/>
@@ -30467,10 +30459,10 @@
         <v>0.63624681809834693</v>
       </c>
       <c r="Z274" s="17">
-        <v>0.65993619738043141</v>
+        <v>0.65951368155906576</v>
       </c>
       <c r="AA274" s="17">
-        <v>0.66076160725975741</v>
+        <v>0.65780966390996265</v>
       </c>
       <c r="AB274" s="9"/>
       <c r="AC274" s="9"/>
@@ -30619,10 +30611,10 @@
         <v>21.322482471046825</v>
       </c>
       <c r="Z275" s="17">
-        <v>21.112700316741513</v>
+        <v>21.127574552216526</v>
       </c>
       <c r="AA275" s="17">
-        <v>22.712951469067001</v>
+        <v>22.719554744976538</v>
       </c>
       <c r="AB275" s="9"/>
       <c r="AC275" s="9"/>
@@ -31183,7 +31175,7 @@
     </row>
     <row r="284" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="286" spans="1:96" x14ac:dyDescent="0.2">
@@ -31193,7 +31185,7 @@
     </row>
     <row r="287" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="288" spans="1:96" x14ac:dyDescent="0.2">
@@ -31395,10 +31387,10 @@
         <v>18.308809392369831</v>
       </c>
       <c r="Z293" s="17">
-        <v>19.283813686131221</v>
+        <v>19.261140789540082</v>
       </c>
       <c r="AA293" s="17">
-        <v>20.969870169865878</v>
+        <v>20.915508258093457</v>
       </c>
       <c r="AB293" s="9"/>
       <c r="AC293" s="9"/>
@@ -31547,10 +31539,10 @@
         <v>10.026542707701783</v>
       </c>
       <c r="Z294" s="17">
-        <v>9.8747792621402706</v>
+        <v>9.8636352425104779</v>
       </c>
       <c r="AA294" s="17">
-        <v>11.244804183440069</v>
+        <v>11.174134875418634</v>
       </c>
       <c r="AB294" s="9"/>
       <c r="AC294" s="9"/>
@@ -31699,10 +31691,10 @@
         <v>2.8823888999294334</v>
       </c>
       <c r="Z295" s="17">
-        <v>3.4981915850304501</v>
+        <v>3.4945412970668706</v>
       </c>
       <c r="AA295" s="17">
-        <v>3.6424080300516435</v>
+        <v>3.6349204446573919</v>
       </c>
       <c r="AB295" s="9"/>
       <c r="AC295" s="9"/>
@@ -31851,10 +31843,10 @@
         <v>0.22077029533739942</v>
       </c>
       <c r="Z296" s="17">
-        <v>0.21331471497021429</v>
+        <v>0.21322352171701969</v>
       </c>
       <c r="AA296" s="17">
-        <v>0.1999817228230896</v>
+        <v>0.20035788753871051</v>
       </c>
       <c r="AB296" s="9"/>
       <c r="AC296" s="9"/>
@@ -32003,10 +31995,10 @@
         <v>0.97304975632459945</v>
       </c>
       <c r="Z297" s="17">
-        <v>1.3932021343651644</v>
+        <v>1.3894825302944245</v>
       </c>
       <c r="AA297" s="17">
-        <v>1.3941488442036016</v>
+        <v>1.4105360925321913</v>
       </c>
       <c r="AB297" s="9"/>
       <c r="AC297" s="9"/>
@@ -32155,10 +32147,10 @@
         <v>1.3447731596867327</v>
       </c>
       <c r="Z298" s="17">
-        <v>1.3921892329509105</v>
+        <v>1.3909500468080127</v>
       </c>
       <c r="AA298" s="17">
-        <v>1.3071200408717807</v>
+        <v>1.3110934311312983</v>
       </c>
       <c r="AB298" s="9"/>
       <c r="AC298" s="9"/>
@@ -32307,10 +32299,10 @@
         <v>1.5794205301579405</v>
       </c>
       <c r="Z299" s="17">
-        <v>1.6103208647252738</v>
+        <v>1.6084616488651278</v>
       </c>
       <c r="AA299" s="17">
-        <v>1.933870910144263</v>
+        <v>1.9317460226161594</v>
       </c>
       <c r="AB299" s="9"/>
       <c r="AC299" s="9"/>
@@ -32459,10 +32451,10 @@
         <v>0.95974361484304704</v>
       </c>
       <c r="Z300" s="17">
-        <v>0.99038612487916977</v>
+        <v>0.9896558839556665</v>
       </c>
       <c r="AA300" s="17">
-        <v>0.94848479566160671</v>
+        <v>0.95172842666798629</v>
       </c>
       <c r="AB300" s="9"/>
       <c r="AC300" s="9"/>
@@ -32611,10 +32603,10 @@
         <v>0.26746114409974941</v>
       </c>
       <c r="Z301" s="17">
-        <v>0.26244533299958045</v>
+        <v>0.26225223727854963</v>
       </c>
       <c r="AA301" s="17">
-        <v>0.24954650008598669</v>
+        <v>0.25132444835224221</v>
       </c>
       <c r="AB301" s="9"/>
       <c r="AC301" s="9"/>
@@ -32763,10 +32755,10 @@
         <v>5.4659284289140374E-2</v>
       </c>
       <c r="Z302" s="17">
-        <v>4.8984434070186586E-2</v>
+        <v>4.8938381043933374E-2</v>
       </c>
       <c r="AA302" s="17">
-        <v>4.9505142583838389E-2</v>
+        <v>4.9666629178845567E-2</v>
       </c>
       <c r="AB302" s="9"/>
       <c r="AC302" s="9"/>
@@ -32915,10 +32907,10 @@
         <v>15.571112888633444</v>
       </c>
       <c r="Z303" s="17">
-        <v>15.359151253346589</v>
+        <v>15.345231609576334</v>
       </c>
       <c r="AA303" s="17">
-        <v>14.418361731102236</v>
+        <v>14.276925100661614</v>
       </c>
       <c r="AB303" s="9"/>
       <c r="AC303" s="9"/>
@@ -33067,10 +33059,10 @@
         <v>4.8470425486963533</v>
       </c>
       <c r="Z304" s="17">
-        <v>4.7341253442132549</v>
+        <v>4.7314276832786701</v>
       </c>
       <c r="AA304" s="17">
-        <v>4.7829853546495</v>
+        <v>4.8269853673858423</v>
       </c>
       <c r="AB304" s="9"/>
       <c r="AC304" s="9"/>
@@ -33219,10 +33211,10 @@
         <v>1.1778769446766217</v>
       </c>
       <c r="Z305" s="17">
-        <v>1.2543194146907244</v>
+        <v>1.2560321570960371</v>
       </c>
       <c r="AA305" s="17">
-        <v>1.0822575182794736</v>
+        <v>1.0990086407683988</v>
       </c>
       <c r="AB305" s="9"/>
       <c r="AC305" s="9"/>
@@ -33371,10 +33363,10 @@
         <v>4.6352633588422494</v>
       </c>
       <c r="Z306" s="17">
-        <v>4.8296185855482028</v>
+        <v>4.8354553529054076</v>
       </c>
       <c r="AA306" s="17">
-        <v>4.2440848900319565</v>
+        <v>4.25766955803243</v>
       </c>
       <c r="AB306" s="9"/>
       <c r="AC306" s="9"/>
@@ -33523,10 +33515,10 @@
         <v>10.455966684040977</v>
       </c>
       <c r="Z307" s="17">
-        <v>8.7819626550078915</v>
+        <v>8.7829447137999868</v>
       </c>
       <c r="AA307" s="17">
-        <v>9.1281360842185926</v>
+        <v>9.2204542650729415</v>
       </c>
       <c r="AB307" s="9"/>
       <c r="AC307" s="9"/>
@@ -33675,10 +33667,10 @@
         <v>1.1770707292229101</v>
       </c>
       <c r="Z308" s="17">
-        <v>1.1616538882352621</v>
+        <v>1.161020108577318</v>
       </c>
       <c r="AA308" s="17">
-        <v>1.0799439692563706</v>
+        <v>1.0963375541319789</v>
       </c>
       <c r="AB308" s="9"/>
       <c r="AC308" s="9"/>
@@ -33827,10 +33819,10 @@
         <v>2.7971706682417827</v>
       </c>
       <c r="Z309" s="17">
-        <v>2.6599460817882852</v>
+        <v>2.6578992882535797</v>
       </c>
       <c r="AA309" s="17">
-        <v>3.199542716501254</v>
+        <v>3.2636738736519497</v>
       </c>
       <c r="AB309" s="9"/>
       <c r="AC309" s="9"/>
@@ -33979,10 +33971,10 @@
         <v>4.7075933471847664</v>
       </c>
       <c r="Z310" s="17">
-        <v>4.7033247360438608</v>
+        <v>4.7017465192057699</v>
       </c>
       <c r="AA310" s="17">
-        <v>4.6642848601025308</v>
+        <v>4.6956327363412234</v>
       </c>
       <c r="AB310" s="9"/>
       <c r="AC310" s="9"/>
@@ -34131,10 +34123,10 @@
         <v>2.2159439161356924</v>
       </c>
       <c r="Z311" s="17">
-        <v>2.8076716634106655</v>
+        <v>2.8042973003495106</v>
       </c>
       <c r="AA311" s="17">
-        <v>2.6199031227322198</v>
+        <v>2.6245271120434994</v>
       </c>
       <c r="AB311" s="9"/>
       <c r="AC311" s="9"/>
@@ -34283,10 +34275,10 @@
         <v>0.84459127960222913</v>
       </c>
       <c r="Z312" s="17">
-        <v>0.84456428752081902</v>
+        <v>0.84354874112766209</v>
       </c>
       <c r="AA312" s="17">
-        <v>0.8080459984782028</v>
+        <v>0.80950487134081561</v>
       </c>
       <c r="AB312" s="9"/>
       <c r="AC312" s="9"/>
@@ -34435,10 +34427,10 @@
         <v>2.6263252927392049</v>
       </c>
       <c r="Z313" s="17">
-        <v>2.8108811246705128</v>
+        <v>2.8080317979724652</v>
       </c>
       <c r="AA313" s="17">
-        <v>2.5606831412931395</v>
+        <v>2.5724599948948357</v>
       </c>
       <c r="AB313" s="9"/>
       <c r="AC313" s="9"/>
@@ -34587,10 +34579,10 @@
         <v>1.0522589710071211</v>
       </c>
       <c r="Z314" s="17">
-        <v>1.0924950950364396</v>
+        <v>1.0913233660912578</v>
       </c>
       <c r="AA314" s="17">
-        <v>0.9904234373988231</v>
+        <v>0.98503141196879784</v>
       </c>
       <c r="AB314" s="9"/>
       <c r="AC314" s="9"/>
@@ -34739,10 +34731,10 @@
         <v>1.139876403354934</v>
       </c>
       <c r="Z315" s="17">
-        <v>1.3348418471065111</v>
+        <v>1.3333661890581738</v>
       </c>
       <c r="AA315" s="17">
-        <v>1.0414678433092253</v>
+        <v>1.0494822199674438</v>
       </c>
       <c r="AB315" s="9"/>
       <c r="AC315" s="9"/>
@@ -34891,10 +34883,10 @@
         <v>1.0018054766833815</v>
       </c>
       <c r="Z316" s="17">
-        <v>0.87817171501765545</v>
+        <v>0.8771423721760182</v>
       </c>
       <c r="AA316" s="17">
-        <v>0.27297983601606335</v>
+        <v>0.27769242155741153</v>
       </c>
       <c r="AB316" s="9"/>
       <c r="AC316" s="9"/>
@@ -35043,10 +35035,10 @@
         <v>1.8354550881519822</v>
       </c>
       <c r="Z317" s="17">
-        <v>1.8779717825180782</v>
+        <v>1.8772038995362041</v>
       </c>
       <c r="AA317" s="17">
-        <v>2.0939421736390775</v>
+        <v>2.1114248381787495</v>
       </c>
       <c r="AB317" s="9"/>
       <c r="AC317" s="9"/>
@@ -35195,10 +35187,10 @@
         <v>2.3483560618909229</v>
       </c>
       <c r="Z318" s="17">
-        <v>2.4855319368141271</v>
+        <v>2.4827811825684494</v>
       </c>
       <c r="AA318" s="17">
-        <v>2.5347180382950198</v>
+        <v>2.5564499777950975</v>
       </c>
       <c r="AB318" s="9"/>
       <c r="AC318" s="9"/>
@@ -35347,10 +35339,10 @@
         <v>1.0078612533492566</v>
       </c>
       <c r="Z319" s="17">
-        <v>1.0110250013298954</v>
+        <v>1.0098285750266773</v>
       </c>
       <c r="AA319" s="17">
-        <v>1.0757482905384008</v>
+        <v>1.0776522617512301</v>
       </c>
       <c r="AB319" s="9"/>
       <c r="AC319" s="9"/>
@@ -35499,10 +35491,10 @@
         <v>1.3859060899843754</v>
       </c>
       <c r="Z320" s="17">
-        <v>1.2479178565891202</v>
+        <v>1.2469562856889016</v>
       </c>
       <c r="AA320" s="17">
-        <v>1.3788003660771304</v>
+        <v>1.3837134208665214</v>
       </c>
       <c r="AB320" s="9"/>
       <c r="AC320" s="9"/>
@@ -35651,10 +35643,10 @@
         <v>1.031985232582298</v>
       </c>
       <c r="Z321" s="17">
-        <v>1.040589178705847</v>
+        <v>1.0394875916248554</v>
       </c>
       <c r="AA321" s="17">
-        <v>1.0348557717777909</v>
+        <v>1.0342595362909019</v>
       </c>
       <c r="AB321" s="9"/>
       <c r="AC321" s="9"/>
@@ -35803,10 +35795,10 @@
         <v>19.831728372609668</v>
       </c>
       <c r="Z322" s="17">
-        <v>19.800422866275031</v>
+        <v>19.853134476546629</v>
       </c>
       <c r="AA322" s="17">
-        <v>20.018964686437108</v>
+        <v>19.865606579204872</v>
       </c>
       <c r="AB322" s="9"/>
       <c r="AC322" s="9"/>
